--- a/public/exports/29189420.xlsx
+++ b/public/exports/29189420.xlsx
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028690</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">

--- a/public/exports/29189420.xlsx
+++ b/public/exports/29189420.xlsx
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">310012628</t>
+          <t xml:space="preserve">310012627</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017950</t>
+          <t xml:space="preserve">310017954</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018570</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018572</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018575</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018567</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020312</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020357</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020321</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020346</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020327</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020360</t>
+          <t xml:space="preserve">310020353</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052073</t>
+          <t xml:space="preserve">311052074</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147497</t>
+          <t xml:space="preserve">311147496</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -22014,7 +22014,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466936</t>
+          <t xml:space="preserve">311466943</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466936</t>
+          <t xml:space="preserve">311466943</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466936</t>
+          <t xml:space="preserve">311466943</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466936</t>
+          <t xml:space="preserve">311466943</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471483</t>
+          <t xml:space="preserve">311471472</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471480</t>
+          <t xml:space="preserve">311471472</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472041</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472041</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472034</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -22734,7 +22734,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472035</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472036</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477935</t>
+          <t xml:space="preserve">311477990</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -25374,7 +25374,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484154</t>
+          <t xml:space="preserve">311484158</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484156</t>
+          <t xml:space="preserve">311484158</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484161</t>
+          <t xml:space="preserve">311484158</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501674</t>
+          <t xml:space="preserve">311501672</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501674</t>
+          <t xml:space="preserve">311501672</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501674</t>
+          <t xml:space="preserve">311501672</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -31434,7 +31434,7 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558281</t>
+          <t xml:space="preserve">311558273</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558281</t>
+          <t xml:space="preserve">311558273</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -31614,7 +31614,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558280</t>
+          <t xml:space="preserve">311558273</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558281</t>
+          <t xml:space="preserve">311558273</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -32034,7 +32034,7 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560887</t>
+          <t xml:space="preserve">311560891</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560886</t>
+          <t xml:space="preserve">311560891</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560887</t>
+          <t xml:space="preserve">311560891</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -33714,7 +33714,7 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568982</t>
+          <t xml:space="preserve">311568985</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
@@ -33774,7 +33774,7 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568982</t>
+          <t xml:space="preserve">311568985</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
@@ -34614,7 +34614,7 @@
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577660</t>
+          <t xml:space="preserve">311577659</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711598</t>
+          <t xml:space="preserve">311711599</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">

--- a/public/exports/29189420.xlsx
+++ b/public/exports/29189420.xlsx
@@ -9414,12 +9414,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017954</t>
+          <t xml:space="preserve">310017950</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10194,12 +10194,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018570</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018572</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018575</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018578</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018578</t>
+          <t xml:space="preserve">310018564</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018539</t>
+          <t xml:space="preserve">310018534</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020300</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020312</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020321</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020292</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020332</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -16954,12 +16954,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17084,12 +17084,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17344,12 +17344,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17409,12 +17409,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -17474,12 +17474,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17539,12 +17539,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -23844,12 +23844,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466943</t>
+          <t xml:space="preserve">311466936</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -23909,12 +23909,12 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466943</t>
+          <t xml:space="preserve">311466936</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
@@ -23974,12 +23974,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466943</t>
+          <t xml:space="preserve">311466936</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -24039,12 +24039,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466943</t>
+          <t xml:space="preserve">311466936</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471483</t>
+          <t xml:space="preserve">311471472</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472041</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472041</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472034</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472036</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -24949,12 +24949,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311474765</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -25014,12 +25014,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311474765</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -25079,12 +25079,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311474765</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -25144,12 +25144,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311474765</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -25209,12 +25209,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311474765</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -25274,12 +25274,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311474765</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477990</t>
+          <t xml:space="preserve">311477935</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -27484,7 +27484,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484158</t>
+          <t xml:space="preserve">311484154</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484158</t>
+          <t xml:space="preserve">311484156</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -27614,7 +27614,7 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484158</t>
+          <t xml:space="preserve">311484157</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -33594,7 +33594,7 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555498</t>
+          <t xml:space="preserve">311555497</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558280</t>
+          <t xml:space="preserve">311558273</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -34634,12 +34634,12 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560894</t>
+          <t xml:space="preserve">311560891</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K533" t="inlineStr">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568869</t>
+          <t xml:space="preserve">311568868</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568985</t>
+          <t xml:space="preserve">311568982</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
@@ -36584,7 +36584,7 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568985</t>
+          <t xml:space="preserve">311568982</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
@@ -36714,7 +36714,7 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568869</t>
+          <t xml:space="preserve">311568866</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
@@ -44514,7 +44514,7 @@
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867792</t>
+          <t xml:space="preserve">311867758</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
